--- a/artfynd/A 23697-2025 artfynd.xlsx
+++ b/artfynd/A 23697-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134057782</v>
       </c>
       <c r="B2" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>134057820</v>
       </c>
       <c r="B3" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23697-2025 artfynd.xlsx
+++ b/artfynd/A 23697-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134057782</v>
+        <v>134057820</v>
       </c>
       <c r="B2" t="n">
-        <v>79366</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387506</v>
+        <v>387514</v>
       </c>
       <c r="R2" t="n">
-        <v>6653029</v>
+        <v>6653003</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134057820</v>
+        <v>134057821</v>
       </c>
       <c r="B3" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387514</v>
+        <v>387471</v>
       </c>
       <c r="R3" t="n">
-        <v>6653003</v>
+        <v>6652967</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,6 +866,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134057781</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björnhöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>387506</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6653029</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
